--- a/companies/ktg/model.xlsx
+++ b/companies/ktg/model.xlsx
@@ -7141,7 +7141,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>71f7a5b927d46a03</t>
+          <t>001bee6946633baa</t>
         </is>
       </c>
     </row>

--- a/companies/ktg/model.xlsx
+++ b/companies/ktg/model.xlsx
@@ -7141,7 +7141,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>001bee6946633baa</t>
+          <t>d05b62086640f711</t>
         </is>
       </c>
     </row>
